--- a/data/trans_dic/P1428-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1428-Edad-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,81</t>
+          <t>0,0; 0,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,23</t>
+          <t>0,0; 1,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,01</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,44</t>
+          <t>0,0; 1,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,97</t>
+          <t>0,56; 6,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,18</t>
+          <t>0,24; 1,22</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,93</t>
+          <t>0,1; 1,07</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,69</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,94</t>
+          <t>0,26; 3,03</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -857,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,18</t>
+          <t>0,14; 1,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,44</t>
+          <t>0,44; 2,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,2</t>
+          <t>0,0; 1,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -877,42 +877,42 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,63</t>
+          <t>0,5; 2,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,54</t>
+          <t>0,16; 1,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>0,0; 1,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,47</t>
+          <t>0,47; 2,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,43</t>
+          <t>0,38; 1,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,67</t>
+          <t>0,46; 1,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,96</t>
+          <t>0,09; 1,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,31</t>
+          <t>0,23; 1,25</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,43</t>
+          <t>0,18; 1,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,09</t>
+          <t>0,41; 1,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,13</t>
+          <t>0,45; 2,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,46</t>
+          <t>0,4; 2,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 7,61</t>
+          <t>4,12; 7,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,23</t>
+          <t>1,07; 3,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,5</t>
+          <t>0,56; 2,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,16</t>
+          <t>1,78; 4,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,21</t>
+          <t>2,4; 4,25</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,28</t>
+          <t>0,92; 2,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,95</t>
+          <t>0,73; 2,06</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,87</t>
+          <t>1,37; 2,82</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,29; 7,16</t>
+          <t>3,19; 7,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,4</t>
+          <t>1,02; 3,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,79</t>
+          <t>2,41; 5,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,87</t>
+          <t>2,55; 5,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,83; 18,04</t>
+          <t>11,51; 17,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,88; 10,35</t>
+          <t>5,72; 10,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,68; 8,74</t>
+          <t>4,81; 8,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,0; 11,6</t>
+          <t>7,04; 10,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,04; 11,95</t>
+          <t>8,01; 11,81</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,69; 6,35</t>
+          <t>3,63; 6,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 6,64</t>
+          <t>3,94; 6,59</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 7,19</t>
+          <t>5,17; 7,4</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,77; 20,6</t>
+          <t>12,84; 20,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,87; 12,78</t>
+          <t>6,6; 12,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,28; 7,49</t>
+          <t>3,18; 7,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,87; 10,11</t>
+          <t>5,69; 9,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,38; 32,28</t>
+          <t>23,8; 32,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,5; 24,07</t>
+          <t>16,44; 24,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,07; 20,04</t>
+          <t>12,81; 19,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,19; 20,98</t>
+          <t>15,86; 20,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,35; 25,45</t>
+          <t>19,52; 25,53</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,47; 17,37</t>
+          <t>12,56; 17,88</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,87; 12,96</t>
+          <t>8,75; 12,76</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,5; 14,78</t>
+          <t>11,35; 14,44</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,4; 26,68</t>
+          <t>17,72; 26,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,24; 21,87</t>
+          <t>12,05; 21,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,74; 10,74</t>
+          <t>4,74; 10,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,08; 13,2</t>
+          <t>7,93; 12,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>41,6; 52,02</t>
+          <t>41,97; 51,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,14; 38,37</t>
+          <t>27,3; 37,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,9; 29,41</t>
+          <t>20,62; 29,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28,97; 81,5</t>
+          <t>27,43; 33,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32,19; 38,95</t>
+          <t>32,07; 39,25</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21,56; 28,8</t>
+          <t>21,91; 28,48</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13,8; 19,47</t>
+          <t>13,71; 19,49</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,98; 68,14</t>
+          <t>18,62; 22,77</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,06%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>28,74; 41,34</t>
+          <t>29,13; 41,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,74; 28,62</t>
+          <t>18,42; 28,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,71; 19,97</t>
+          <t>11,6; 19,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,54; 25,43</t>
+          <t>17,42; 24,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>53,45; 65,22</t>
+          <t>53,57; 64,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,71; 48,19</t>
+          <t>37,54; 47,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,03; 30,66</t>
+          <t>21,06; 30,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>39,65; 46,37</t>
+          <t>39,56; 46,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>45,24; 54,07</t>
+          <t>45,4; 54,5</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30,96; 38,7</t>
+          <t>31,01; 39,16</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,35; 24,9</t>
+          <t>18,44; 25,31</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>31,71; 36,87</t>
+          <t>31,4; 36,8</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,37; 8,15</t>
+          <t>6,46; 8,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,42; 5,99</t>
+          <t>4,41; 6,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,99; 4,3</t>
+          <t>2,96; 4,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,95; 5,87</t>
+          <t>4,55; 5,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,34; 18,97</t>
+          <t>16,39; 19,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,2; 13,51</t>
+          <t>11,3; 13,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,36; 10,45</t>
+          <t>8,41; 10,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,95; 36,3</t>
+          <t>13,47; 15,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11,68; 13,36</t>
+          <t>11,69; 13,37</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8,16; 9,57</t>
+          <t>8,2; 9,62</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,88; 7,16</t>
+          <t>5,94; 7,12</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,32; 24,01</t>
+          <t>9,31; 10,46</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>7844</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>7844</t>
         </is>
       </c>
     </row>
@@ -2068,12 +2068,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>856; 9022</t>
+          <t>861; 9056</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3685</t>
+          <t>0; 4197</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -2088,42 +2088,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5735</t>
+          <t>0; 6720</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 8654</t>
+          <t>0; 7689</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5680</t>
+          <t>0; 5676</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1587; 18688</t>
+          <t>2041; 21986</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1938; 11379</t>
+          <t>2343; 11759</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>906; 8248</t>
+          <t>910; 9470</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5671</t>
+          <t>0; 5665</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1604; 20958</t>
+          <t>2026; 23334</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>6129</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>6129</t>
         </is>
       </c>
     </row>
@@ -2276,17 +2276,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1015; 8704</t>
+          <t>1009; 8427</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3003; 16758</t>
+          <t>3052; 18528</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 7087</t>
+          <t>0; 6219</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2296,42 +2296,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3523; 16471</t>
+          <t>3144; 16795</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>972; 9373</t>
+          <t>967; 8727</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 9653</t>
+          <t>0; 9317</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1740; 12633</t>
+          <t>2340; 12348</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5681; 19530</t>
+          <t>5137; 19439</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5869; 21601</t>
+          <t>5912; 21039</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1057; 11026</t>
+          <t>1059; 11571</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1985; 12236</t>
+          <t>2206; 12233</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>6870</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15314</t>
+          <t>17737</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21315</t>
+          <t>24607</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1102; 9126</t>
+          <t>1129; 9717</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2823; 14281</t>
+          <t>2804; 13085</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2930; 14221</t>
+          <t>2980; 15670</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2193; 13150</t>
+          <t>2471; 14031</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27891; 52502</t>
+          <t>28403; 52328</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7733; 22889</t>
+          <t>7614; 22502</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3746; 16523</t>
+          <t>3681; 16199</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10108; 22508</t>
+          <t>11031; 25284</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31113; 55894</t>
+          <t>31842; 56454</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13622; 31785</t>
+          <t>12744; 30868</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8988; 25893</t>
+          <t>9648; 27400</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14681; 30873</t>
+          <t>17026; 34952</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26404</t>
+          <t>26615</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>62229</t>
+          <t>62270</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88633</t>
+          <t>88885</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17055; 37184</t>
+          <t>16561; 37098</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5425; 20876</t>
+          <t>6239; 20551</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16506; 37430</t>
+          <t>15576; 36637</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10253; 43140</t>
+          <t>17775; 39085</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>61004; 93043</t>
+          <t>59338; 90868</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36090; 63592</t>
+          <t>35165; 62961</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30377; 56703</t>
+          <t>31250; 57347</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>49425; 81906</t>
+          <t>51352; 74786</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>83178; 123687</t>
+          <t>82895; 122230</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>45297; 78077</t>
+          <t>44641; 78212</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52275; 85984</t>
+          <t>51044; 85290</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>54930; 114463</t>
+          <t>73861; 105667</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43763</t>
+          <t>45117</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>100330</t>
+          <t>110249</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>144093</t>
+          <t>155366</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>49400; 79659</t>
+          <t>49639; 78839</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>29487; 54861</t>
+          <t>28328; 53352</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15671; 35815</t>
+          <t>15214; 36662</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32843; 56550</t>
+          <t>34572; 59843</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>94435; 130397</t>
+          <t>96165; 131381</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>73868; 107780</t>
+          <t>73626; 108752</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>64961; 99581</t>
+          <t>63666; 97660</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>87864; 113824</t>
+          <t>95777; 124523</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>153037; 201263</t>
+          <t>154328; 201836</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>109376; 152344</t>
+          <t>110149; 156826</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>86464; 126340</t>
+          <t>85279; 124399</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>126713; 162810</t>
+          <t>137467; 174869</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38375</t>
+          <t>41640</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>325158</t>
+          <t>132410</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>363533</t>
+          <t>174050</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>50908; 78066</t>
+          <t>51860; 77892</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>37919; 67747</t>
+          <t>37320; 66232</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15863; 35903</t>
+          <t>15849; 35275</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29635; 48406</t>
+          <t>32138; 51920</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>142654; 178411</t>
+          <t>143933; 177656</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>99603; 135828</t>
+          <t>96657; 132457</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>78970; 111100</t>
+          <t>77894; 111085</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>175910; 494866</t>
+          <t>120096; 148098</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>204594; 247507</t>
+          <t>203789; 249440</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>143100; 191143</t>
+          <t>145416; 189024</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>98268; 138628</t>
+          <t>97609; 138784</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>194559; 663497</t>
+          <t>156993; 191965</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>59022</t>
+          <t>64865</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>181840</t>
+          <t>198128</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>240862</t>
+          <t>262993</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>60322; 86761</t>
+          <t>61140; 86689</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>44321; 71516</t>
+          <t>46019; 72247</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30094; 51334</t>
+          <t>29811; 49422</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49456; 71703</t>
+          <t>53883; 76983</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>178486; 217779</t>
+          <t>178872; 216767</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>146701; 187440</t>
+          <t>146015; 185909</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>84142; 122708</t>
+          <t>84294; 123300</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>168258; 196774</t>
+          <t>183164; 213657</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>246019; 294001</t>
+          <t>246896; 296389</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>197790; 247209</t>
+          <t>198112; 250176</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>120593; 163621</t>
+          <t>121208; 166351</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>223963; 260380</t>
+          <t>242468; 284186</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>173564</t>
+          <t>185107</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>697191</t>
+          <t>534768</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>870755</t>
+          <t>719874</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>208868; 267097</t>
+          <t>211644; 267642</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>151392; 205192</t>
+          <t>150975; 206819</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>101492; 146115</t>
+          <t>100603; 145592</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>136351; 202713</t>
+          <t>160410; 210735</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>552263; 640890</t>
+          <t>553969; 642144</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>398302; 480345</t>
+          <t>401719; 481574</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>296250; 370515</t>
+          <t>298270; 371859</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>508592; 1323440</t>
+          <t>500818; 566276</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>777516; 889127</t>
+          <t>778081; 889635</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>569815; 668340</t>
+          <t>572809; 671632</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>408237; 496976</t>
+          <t>412329; 494081</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>661515; 1704021</t>
+          <t>673935; 757593</t>
         </is>
       </c>
     </row>
